--- a/s1.xlsx
+++ b/s1.xlsx
@@ -540,7 +540,7 @@
         <v>233694.85793966</v>
       </c>
       <c r="L2" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M2" t="n">
         <v>-509548890.4653558</v>
@@ -587,7 +587,7 @@
         <v>223128.4444691042</v>
       </c>
       <c r="L3" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M3" t="n">
         <v>-509547610.9435556</v>
@@ -634,7 +634,7 @@
         <v>211632.5715864964</v>
       </c>
       <c r="L4" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M4" t="n">
         <v>-509546163.7210801</v>
@@ -681,7 +681,7 @@
         <v>199417.005034447</v>
       </c>
       <c r="L5" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M5" t="n">
         <v>-509544372.6440705</v>
@@ -728,7 +728,7 @@
         <v>186518.5104054274</v>
       </c>
       <c r="L6" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M6" t="n">
         <v>-509542059.8560176</v>
@@ -775,7 +775,7 @@
         <v>172930.6840219487</v>
       </c>
       <c r="L7" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M7" t="n">
         <v>-509539104.1196195</v>
@@ -822,7 +822,7 @@
         <v>158644.0099942044</v>
       </c>
       <c r="L8" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M8" t="n">
         <v>-509535460.1490543</v>
@@ -869,7 +869,7 @@
         <v>143648.0324346543</v>
       </c>
       <c r="L9" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M9" t="n">
         <v>-509531140.1666386</v>
@@ -916,7 +916,7 @@
         <v>127932.4450437825</v>
       </c>
       <c r="L10" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M10" t="n">
         <v>-509526188.478286</v>
@@ -963,7 +963,7 @@
         <v>111495.0090830158</v>
       </c>
       <c r="L11" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M11" t="n">
         <v>-509520662.1791348</v>
@@ -1010,7 +1010,7 @@
         <v>94347.50764057937</v>
       </c>
       <c r="L12" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M12" t="n">
         <v>-509514619.6508754</v>
@@ -1057,7 +1057,7 @@
         <v>76516.80387582449</v>
       </c>
       <c r="L13" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M13" t="n">
         <v>-509508114.9260817</v>
@@ -1104,7 +1104,7 @@
         <v>58042.9475477603</v>
       </c>
       <c r="L14" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M14" t="n">
         <v>-509501195.6470088</v>
@@ -1151,7 +1151,7 @@
         <v>38975.96949735028</v>
       </c>
       <c r="L15" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M15" t="n">
         <v>-509493902.9156761</v>
@@ -1198,7 +1198,7 @@
         <v>19372.12434897479</v>
       </c>
       <c r="L16" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M16" t="n">
         <v>-509486271.9746082</v>
@@ -1245,7 +1245,7 @@
         <v>-709.9086374894832</v>
       </c>
       <c r="L17" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M17" t="n">
         <v>-509478333.1384051</v>
@@ -1292,7 +1292,7 @@
         <v>-21212.43608556379</v>
       </c>
       <c r="L18" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M18" t="n">
         <v>-509470112.6990705</v>
@@ -1339,7 +1339,7 @@
         <v>-42081.4637164211</v>
       </c>
       <c r="L19" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M19" t="n">
         <v>-509461633.6976554</v>
@@ -1386,7 +1386,7 @@
         <v>-63268.55610866094</v>
       </c>
       <c r="L20" t="n">
-        <v>-194.1695245173063</v>
+        <v>-509792086.6201878</v>
       </c>
       <c r="M20" t="n">
         <v>-509452916.539914</v>
